--- a/Shiny/Datos limpios/pricing_diario_maiz_2025.xlsx
+++ b/Shiny/Datos limpios/pricing_diario_maiz_2025.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K276"/>
+  <dimension ref="A1:K300"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -10561,19 +10561,19 @@
         <v>45957</v>
       </c>
       <c r="B276">
-        <v>1510</v>
+        <v>53856.24</v>
       </c>
       <c r="C276">
-        <v>0</v>
+        <v>658.8200000000001</v>
       </c>
       <c r="D276">
-        <v>0</v>
+        <v>862.59</v>
       </c>
       <c r="E276">
-        <v>1510</v>
+        <v>53652.47</v>
       </c>
       <c r="F276">
-        <v>0</v>
+        <v>10947.52</v>
       </c>
       <c r="G276">
         <v>0</v>
@@ -10582,12 +10582,900 @@
         <v>0</v>
       </c>
       <c r="I276">
-        <v>0</v>
+        <v>10947.52</v>
       </c>
       <c r="J276">
-        <v>1510</v>
+        <v>64599.99000000001</v>
       </c>
       <c r="K276" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B277">
+        <v>100329.19</v>
+      </c>
+      <c r="C277">
+        <v>2478.38</v>
+      </c>
+      <c r="D277">
+        <v>0</v>
+      </c>
+      <c r="E277">
+        <v>102807.57</v>
+      </c>
+      <c r="F277">
+        <v>14310.69</v>
+      </c>
+      <c r="G277">
+        <v>0</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+      <c r="I277">
+        <v>14310.69</v>
+      </c>
+      <c r="J277">
+        <v>117118.26</v>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B278">
+        <v>55249.1</v>
+      </c>
+      <c r="C278">
+        <v>270.16</v>
+      </c>
+      <c r="D278">
+        <v>210.16</v>
+      </c>
+      <c r="E278">
+        <v>55309.1</v>
+      </c>
+      <c r="F278">
+        <v>40061.28</v>
+      </c>
+      <c r="G278">
+        <v>100</v>
+      </c>
+      <c r="H278">
+        <v>0</v>
+      </c>
+      <c r="I278">
+        <v>40161.28</v>
+      </c>
+      <c r="J278">
+        <v>95470.38</v>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B279">
+        <v>74464.46000000001</v>
+      </c>
+      <c r="C279">
+        <v>161.33</v>
+      </c>
+      <c r="D279">
+        <v>1100</v>
+      </c>
+      <c r="E279">
+        <v>73525.79000000001</v>
+      </c>
+      <c r="F279">
+        <v>56677.22</v>
+      </c>
+      <c r="G279">
+        <v>0</v>
+      </c>
+      <c r="H279">
+        <v>0</v>
+      </c>
+      <c r="I279">
+        <v>56677.22</v>
+      </c>
+      <c r="J279">
+        <v>130203.01</v>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B280">
+        <v>89175.99000000001</v>
+      </c>
+      <c r="C280">
+        <v>1590</v>
+      </c>
+      <c r="D280">
+        <v>34.51</v>
+      </c>
+      <c r="E280">
+        <v>90731.48000000001</v>
+      </c>
+      <c r="F280">
+        <v>58011.74</v>
+      </c>
+      <c r="G280">
+        <v>2000</v>
+      </c>
+      <c r="H280">
+        <v>4000</v>
+      </c>
+      <c r="I280">
+        <v>56011.74</v>
+      </c>
+      <c r="J280">
+        <v>146743.22</v>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B281">
+        <v>159.87</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>0</v>
+      </c>
+      <c r="E281">
+        <v>159.87</v>
+      </c>
+      <c r="F281">
+        <v>0</v>
+      </c>
+      <c r="G281">
+        <v>0</v>
+      </c>
+      <c r="H281">
+        <v>0</v>
+      </c>
+      <c r="I281">
+        <v>0</v>
+      </c>
+      <c r="J281">
+        <v>159.87</v>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2">
+        <v>45963</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>0</v>
+      </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
+      <c r="F282">
+        <v>0</v>
+      </c>
+      <c r="G282">
+        <v>0</v>
+      </c>
+      <c r="H282">
+        <v>0</v>
+      </c>
+      <c r="I282">
+        <v>0</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B283">
+        <v>84486.81</v>
+      </c>
+      <c r="C283">
+        <v>2034.51</v>
+      </c>
+      <c r="D283">
+        <v>700</v>
+      </c>
+      <c r="E283">
+        <v>85821.31999999999</v>
+      </c>
+      <c r="F283">
+        <v>51734.77</v>
+      </c>
+      <c r="G283">
+        <v>0</v>
+      </c>
+      <c r="H283">
+        <v>300</v>
+      </c>
+      <c r="I283">
+        <v>51434.77</v>
+      </c>
+      <c r="J283">
+        <v>137256.09</v>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B284">
+        <v>75165.13</v>
+      </c>
+      <c r="C284">
+        <v>1477.26</v>
+      </c>
+      <c r="D284">
+        <v>237.69</v>
+      </c>
+      <c r="E284">
+        <v>76404.7</v>
+      </c>
+      <c r="F284">
+        <v>24350.74</v>
+      </c>
+      <c r="G284">
+        <v>0</v>
+      </c>
+      <c r="H284">
+        <v>0</v>
+      </c>
+      <c r="I284">
+        <v>24350.74</v>
+      </c>
+      <c r="J284">
+        <v>100755.44</v>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B285">
+        <v>246117.89</v>
+      </c>
+      <c r="C285">
+        <v>4304</v>
+      </c>
+      <c r="D285">
+        <v>2995.04</v>
+      </c>
+      <c r="E285">
+        <v>247426.85</v>
+      </c>
+      <c r="F285">
+        <v>48673.81</v>
+      </c>
+      <c r="G285">
+        <v>65</v>
+      </c>
+      <c r="H285">
+        <v>410</v>
+      </c>
+      <c r="I285">
+        <v>48328.81</v>
+      </c>
+      <c r="J285">
+        <v>295755.66</v>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B286">
+        <v>180382.21</v>
+      </c>
+      <c r="C286">
+        <v>5297.9</v>
+      </c>
+      <c r="D286">
+        <v>1240</v>
+      </c>
+      <c r="E286">
+        <v>184440.11</v>
+      </c>
+      <c r="F286">
+        <v>22386.36</v>
+      </c>
+      <c r="G286">
+        <v>6000</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+      <c r="I286">
+        <v>28386.36</v>
+      </c>
+      <c r="J286">
+        <v>212826.47</v>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B287">
+        <v>107125.03</v>
+      </c>
+      <c r="C287">
+        <v>1639.84</v>
+      </c>
+      <c r="D287">
+        <v>6240</v>
+      </c>
+      <c r="E287">
+        <v>102524.87</v>
+      </c>
+      <c r="F287">
+        <v>24535.71</v>
+      </c>
+      <c r="G287">
+        <v>0</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+      <c r="I287">
+        <v>24535.71</v>
+      </c>
+      <c r="J287">
+        <v>127060.58</v>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2">
+        <v>45969</v>
+      </c>
+      <c r="B288">
+        <v>516.72</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>0</v>
+      </c>
+      <c r="E288">
+        <v>516.72</v>
+      </c>
+      <c r="F288">
+        <v>0</v>
+      </c>
+      <c r="G288">
+        <v>0</v>
+      </c>
+      <c r="H288">
+        <v>0</v>
+      </c>
+      <c r="I288">
+        <v>0</v>
+      </c>
+      <c r="J288">
+        <v>516.72</v>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2">
+        <v>45970</v>
+      </c>
+      <c r="B289">
+        <v>35</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>0</v>
+      </c>
+      <c r="E289">
+        <v>35</v>
+      </c>
+      <c r="F289">
+        <v>0</v>
+      </c>
+      <c r="G289">
+        <v>0</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+      <c r="I289">
+        <v>0</v>
+      </c>
+      <c r="J289">
+        <v>35</v>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B290">
+        <v>141574.79</v>
+      </c>
+      <c r="C290">
+        <v>517.5700000000001</v>
+      </c>
+      <c r="D290">
+        <v>17620</v>
+      </c>
+      <c r="E290">
+        <v>124472.36</v>
+      </c>
+      <c r="F290">
+        <v>23024.65</v>
+      </c>
+      <c r="G290">
+        <v>0</v>
+      </c>
+      <c r="H290">
+        <v>150</v>
+      </c>
+      <c r="I290">
+        <v>22874.65</v>
+      </c>
+      <c r="J290">
+        <v>147347.01</v>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B291">
+        <v>156223.2</v>
+      </c>
+      <c r="C291">
+        <v>846.9399999999999</v>
+      </c>
+      <c r="D291">
+        <v>2150</v>
+      </c>
+      <c r="E291">
+        <v>154920.14</v>
+      </c>
+      <c r="F291">
+        <v>32333.31</v>
+      </c>
+      <c r="G291">
+        <v>0</v>
+      </c>
+      <c r="H291">
+        <v>30</v>
+      </c>
+      <c r="I291">
+        <v>32303.31</v>
+      </c>
+      <c r="J291">
+        <v>187223.45</v>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B292">
+        <v>107741.54</v>
+      </c>
+      <c r="C292">
+        <v>857</v>
+      </c>
+      <c r="D292">
+        <v>2700</v>
+      </c>
+      <c r="E292">
+        <v>105898.54</v>
+      </c>
+      <c r="F292">
+        <v>17084.26</v>
+      </c>
+      <c r="G292">
+        <v>0</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+      <c r="I292">
+        <v>17084.26</v>
+      </c>
+      <c r="J292">
+        <v>122982.8</v>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B293">
+        <v>165783.29</v>
+      </c>
+      <c r="C293">
+        <v>668.0700000000001</v>
+      </c>
+      <c r="D293">
+        <v>1230</v>
+      </c>
+      <c r="E293">
+        <v>165221.36</v>
+      </c>
+      <c r="F293">
+        <v>30279.37</v>
+      </c>
+      <c r="G293">
+        <v>204.23</v>
+      </c>
+      <c r="H293">
+        <v>480</v>
+      </c>
+      <c r="I293">
+        <v>30003.6</v>
+      </c>
+      <c r="J293">
+        <v>195224.96</v>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B294">
+        <v>321355.95</v>
+      </c>
+      <c r="C294">
+        <v>2018.02</v>
+      </c>
+      <c r="D294">
+        <v>4047.65</v>
+      </c>
+      <c r="E294">
+        <v>319326.32</v>
+      </c>
+      <c r="F294">
+        <v>40314.05</v>
+      </c>
+      <c r="G294">
+        <v>0</v>
+      </c>
+      <c r="H294">
+        <v>0</v>
+      </c>
+      <c r="I294">
+        <v>40314.05</v>
+      </c>
+      <c r="J294">
+        <v>359640.37</v>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2">
+        <v>45976</v>
+      </c>
+      <c r="B295">
+        <v>1709.34</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>0</v>
+      </c>
+      <c r="E295">
+        <v>1709.34</v>
+      </c>
+      <c r="F295">
+        <v>67.13</v>
+      </c>
+      <c r="G295">
+        <v>0</v>
+      </c>
+      <c r="H295">
+        <v>0</v>
+      </c>
+      <c r="I295">
+        <v>67.13</v>
+      </c>
+      <c r="J295">
+        <v>1776.47</v>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B296">
+        <v>85659.13</v>
+      </c>
+      <c r="C296">
+        <v>781.28</v>
+      </c>
+      <c r="D296">
+        <v>2330</v>
+      </c>
+      <c r="E296">
+        <v>84110.41</v>
+      </c>
+      <c r="F296">
+        <v>30464.67</v>
+      </c>
+      <c r="G296">
+        <v>0</v>
+      </c>
+      <c r="H296">
+        <v>630</v>
+      </c>
+      <c r="I296">
+        <v>29834.67</v>
+      </c>
+      <c r="J296">
+        <v>113945.08</v>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B297">
+        <v>59922.54</v>
+      </c>
+      <c r="C297">
+        <v>3606.12</v>
+      </c>
+      <c r="D297">
+        <v>446.2</v>
+      </c>
+      <c r="E297">
+        <v>63082.46000000001</v>
+      </c>
+      <c r="F297">
+        <v>17647.37</v>
+      </c>
+      <c r="G297">
+        <v>150</v>
+      </c>
+      <c r="H297">
+        <v>0</v>
+      </c>
+      <c r="I297">
+        <v>17797.37</v>
+      </c>
+      <c r="J297">
+        <v>80879.83</v>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B298">
+        <v>85408.49000000001</v>
+      </c>
+      <c r="C298">
+        <v>3900.48</v>
+      </c>
+      <c r="D298">
+        <v>1029.23</v>
+      </c>
+      <c r="E298">
+        <v>88279.74000000001</v>
+      </c>
+      <c r="F298">
+        <v>25535.4</v>
+      </c>
+      <c r="G298">
+        <v>3.25</v>
+      </c>
+      <c r="H298">
+        <v>0</v>
+      </c>
+      <c r="I298">
+        <v>25538.65</v>
+      </c>
+      <c r="J298">
+        <v>113818.39</v>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B299">
+        <v>40224.85</v>
+      </c>
+      <c r="C299">
+        <v>170.34</v>
+      </c>
+      <c r="D299">
+        <v>0</v>
+      </c>
+      <c r="E299">
+        <v>40395.19</v>
+      </c>
+      <c r="F299">
+        <v>28373.17</v>
+      </c>
+      <c r="G299">
+        <v>0</v>
+      </c>
+      <c r="H299">
+        <v>0</v>
+      </c>
+      <c r="I299">
+        <v>28373.17</v>
+      </c>
+      <c r="J299">
+        <v>68768.36</v>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B300">
+        <v>5254.32</v>
+      </c>
+      <c r="C300">
+        <v>120</v>
+      </c>
+      <c r="D300">
+        <v>0</v>
+      </c>
+      <c r="E300">
+        <v>5374.32</v>
+      </c>
+      <c r="F300">
+        <v>1674.99</v>
+      </c>
+      <c r="G300">
+        <v>0</v>
+      </c>
+      <c r="H300">
+        <v>0</v>
+      </c>
+      <c r="I300">
+        <v>1674.99</v>
+      </c>
+      <c r="J300">
+        <v>7049.309999999999</v>
+      </c>
+      <c r="K300" t="inlineStr">
         <is>
           <t>MAIZ</t>
         </is>
